--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128042737</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128042738</v>
+        <v>128042740</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467550</v>
+        <v>467374</v>
       </c>
       <c r="R7" t="n">
-        <v>7057073</v>
+        <v>7057153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128042740</v>
+        <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467374</v>
+        <v>467550</v>
       </c>
       <c r="R8" t="n">
-        <v>7057153</v>
+        <v>7057073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128042737</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128042740</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128042737</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128042740</v>
+        <v>128042738</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467374</v>
+        <v>467550</v>
       </c>
       <c r="R7" t="n">
-        <v>7057153</v>
+        <v>7057073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128042738</v>
+        <v>128042740</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467550</v>
+        <v>467374</v>
       </c>
       <c r="R8" t="n">
-        <v>7057073</v>
+        <v>7057153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128042738</v>
+        <v>128042740</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467550</v>
+        <v>467374</v>
       </c>
       <c r="R7" t="n">
-        <v>7057073</v>
+        <v>7057153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128042740</v>
+        <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467374</v>
+        <v>467550</v>
       </c>
       <c r="R8" t="n">
-        <v>7057153</v>
+        <v>7057073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128042737</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128042740</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128042737</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128042740</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128042739</v>
       </c>
       <c r="B2" t="n">
-        <v>91460</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128042737</v>
+        <v>128042740</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467597</v>
+        <v>467374</v>
       </c>
       <c r="R3" t="n">
-        <v>7057093</v>
+        <v>7057153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,11 +877,11 @@
         <v>128042741</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -979,11 +979,11 @@
         <v>128042742</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1081,7 +1081,7 @@
         <v>128042736</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128042740</v>
+        <v>128042737</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467374</v>
+        <v>467597</v>
       </c>
       <c r="R7" t="n">
-        <v>7057153</v>
+        <v>7057093</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>128042738</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36009-2025 artfynd.xlsx
+++ b/artfynd/A 36009-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042740</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042741</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042742</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042736</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042737</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,8 +1416,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128042738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>